--- a/static/template/Draft Output.xlsx
+++ b/static/template/Draft Output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anagaghaisan/New-Compare-Excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anagaghaisan/Excel_Compare/static/template/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D76163-0692-C04C-915E-61D4CF156791}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90722D03-761F-0B42-A6D7-73658ABC502E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17860" xr2:uid="{6518FBC7-83DD-4BC9-842C-15F4FEE7B669}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17840" xr2:uid="{6518FBC7-83DD-4BC9-842C-15F4FEE7B669}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Account Name</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Keterangan (Digunggung/Tidak Digunggung)</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -511,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4546B0E5-70EA-4D1A-B9E8-226BE0C38ECA}">
-  <dimension ref="A2:S4"/>
+  <dimension ref="A2:T4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -535,7 +538,7 @@
     <col min="19" max="19" width="40.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -558,7 +561,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="4" spans="1:19" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" s="4" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
@@ -613,6 +616,9 @@
       </c>
       <c r="S4" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
